--- a/card_definitions.xlsx
+++ b/card_definitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tuiko\remake_project\remake project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99465A69-CF9C-410F-90A6-EB525E706FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A6D518-B5A1-4A4F-846C-0786C126FCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="38700" windowHeight="18780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -758,7 +758,7 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>7</v>
@@ -779,7 +779,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -835,17 +835,17 @@
         <v>19</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
         <v>4</v>
-      </c>
-      <c r="J8">
-        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -856,17 +856,17 @@
         <v>19</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
         <v>7</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -884,10 +884,10 @@
         <v>7.5</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -898,17 +898,17 @@
         <v>22</v>
       </c>
       <c r="C11">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -919,23 +919,23 @@
         <v>16</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H12">
         <f t="shared" si="0"/>
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>6</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -950,7 +950,7 @@
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>3</v>
@@ -978,14 +978,14 @@
         <v>63</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <f t="shared" ref="H15:H37" si="1">IFERROR(VLOOKUP(B15,Prices,2,0)*ABS(C15),0)+IFERROR(VLOOKUP(D15,Prices,2,0)*ABS(E15),0)+IFERROR(VLOOKUP(F15,Prices,2,0)*ABS(G15),0)</f>
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>3</v>
@@ -1012,7 +1012,7 @@
         <v>5.5</v>
       </c>
       <c r="I16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>3</v>
@@ -1026,7 +1026,7 @@
         <v>16</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>62</v>
@@ -1042,13 +1042,13 @@
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="I17">
         <v>4</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1066,10 +1066,10 @@
         <v>7.5</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1093,7 +1093,7 @@
         <v>4</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>3</v>
@@ -1128,17 +1128,17 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <f t="shared" si="1"/>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1225,17 +1225,17 @@
         <v>66</v>
       </c>
       <c r="E25">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H25">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I25">
         <v>4</v>
       </c>
       <c r="J25">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1267,23 +1267,23 @@
         <v>71</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E27">
+        <v>5</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="I27">
+        <v>5</v>
+      </c>
+      <c r="J27">
         <v>4</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="1"/>
-        <v>12.4</v>
-      </c>
-      <c r="I27">
-        <v>5</v>
-      </c>
-      <c r="J27">
-        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1307,10 +1307,10 @@
         <v>3</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1334,7 +1334,7 @@
         <v>2.5</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="H31">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1402,11 +1402,11 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H32">
         <f>IFERROR(VLOOKUP(B32,Prices,2,0)*ABS(C32),0)+IFERROR(VLOOKUP(D32,Prices,2,0)*ABS(E32),0)+IFERROR(VLOOKUP(F32,Prices,2,0)*ABS(G32),0)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>5</v>
@@ -1444,17 +1444,17 @@
         <v>74</v>
       </c>
       <c r="C34">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H34">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1471,11 +1471,11 @@
         <v>68</v>
       </c>
       <c r="E35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H35">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I35">
         <v>20</v>
@@ -1492,20 +1492,20 @@
         <v>72</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H36">
         <f t="shared" si="1"/>
-        <v>11.2</v>
+        <v>12.600000000000001</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -1519,14 +1519,14 @@
         <v>76</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>2</v>
@@ -1576,7 +1576,7 @@
         <v>56</v>
       </c>
       <c r="B4">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1624,7 +1624,7 @@
         <v>26</v>
       </c>
       <c r="B10">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
